--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hatch Yard\Personal-Expense-Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{467898FC-F2E2-4E4D-BBC7-5532F96A3C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75167E80-A9AF-4148-9AEA-9406745AC2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F510D79B-9790-451C-9726-7557C34B427F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -51,13 +51,40 @@
   </si>
   <si>
     <t>Ai prompts</t>
+  </si>
+  <si>
+    <t>x`</t>
+  </si>
+  <si>
+    <t>Set up backend</t>
+  </si>
+  <si>
+    <t>Set up vitest</t>
+  </si>
+  <si>
+    <t>Postgre db configure</t>
+  </si>
+  <si>
+    <t>schema Definition</t>
+  </si>
+  <si>
+    <t>index.ts,app.ts, index.ts, schema.ts, expenses.test.ts</t>
+  </si>
+  <si>
+    <t>Recommend a good project to start with Node.js, TypeScript, Vitest, Drizzle ORM, and React (no Angular).</t>
+  </si>
+  <si>
+    <t>Is this package.json correct?</t>
+  </si>
+  <si>
+    <t>Give me updated app.ts and index.ts.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,16 +92,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -82,12 +129,139 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -103,19 +277,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7DB7065D-8810-42E7-978B-52B94B874843}" name="Table1" displayName="Table1" ref="A3:D18" totalsRowShown="0">
-  <autoFilter ref="A3:D18" xr:uid="{7DB7065D-8810-42E7-978B-52B94B874843}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6F426F65-789C-4BC0-B28B-66C0D7ACDFF8}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{39B688D0-C828-4C9C-9C7C-3377F1D8C2EA}" name="Tasks"/>
-    <tableColumn id="3" xr3:uid="{AB33711B-366F-46E0-897D-30B6329A4389}" name="files"/>
-    <tableColumn id="4" xr3:uid="{2C0608A1-339F-4C69-940C-4E58766A9BAE}" name="Ai prompts"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,35 +596,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C7A0FE-D686-4FF6-9C26-25578A769F5F}">
-  <dimension ref="A3:D3"/>
+  <dimension ref="A3:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="1"/>
-    <col min="2" max="2" width="64.88671875" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="64.5546875" customWidth="1"/>
+    <col min="4" max="4" width="93" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>46309</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="A4:A7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
